--- a/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
+++ b/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
@@ -1151,14 +1151,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45184.56808412736</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="18">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -1204,8 +1200,6 @@
       </c>
       <c r="E11" s="14" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
@@ -1213,12 +1207,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
@@ -1226,15 +1214,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="18" customHeight="1" s="18">
       <c r="A31" s="15" t="inlineStr">
         <is>
@@ -1266,7 +1245,7 @@
       </c>
       <c r="C32" s="20" t="n"/>
       <c r="D32" s="8" t="n">
-        <v>5250</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="18">
@@ -1282,7 +1261,7 @@
       </c>
       <c r="C33" s="20" t="n"/>
       <c r="D33" s="10" t="n">
-        <v>4170</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="18">
@@ -1298,7 +1277,7 @@
       </c>
       <c r="C34" s="20" t="n"/>
       <c r="D34" s="8" t="n">
-        <v>4160</v>
+        <v>4576</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="18">
@@ -1314,7 +1293,7 @@
       </c>
       <c r="C35" s="20" t="n"/>
       <c r="D35" s="8" t="n">
-        <v>5985</v>
+        <v>6583.5</v>
       </c>
     </row>
     <row r="36">
@@ -1324,10 +1303,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -1335,14 +1310,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
     <row r="50" ht="15.75" customHeight="1" s="18">
       <c r="A50" s="4" t="n"/>
     </row>
@@ -1351,16 +1318,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
+++ b/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
@@ -1151,7 +1151,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
+++ b/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
@@ -1151,7 +1151,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
+++ b/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
@@ -1151,7 +1151,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
+++ b/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
@@ -1151,7 +1151,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
+++ b/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
@@ -1151,7 +1151,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
+++ b/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
@@ -1151,10 +1151,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45267</v>
+        <v>45257.55651496706</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="18">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -1200,6 +1204,8 @@
       </c>
       <c r="E11" s="14" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
@@ -1207,6 +1213,12 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
@@ -1214,6 +1226,15 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31" ht="18" customHeight="1" s="18">
       <c r="A31" s="15" t="inlineStr">
         <is>
@@ -1245,7 +1266,7 @@
       </c>
       <c r="C32" s="20" t="n"/>
       <c r="D32" s="8" t="n">
-        <v>5775</v>
+        <v>8370.049999999999</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="18">
@@ -1261,7 +1282,7 @@
       </c>
       <c r="C33" s="20" t="n"/>
       <c r="D33" s="10" t="n">
-        <v>4587</v>
+        <v>6648.21</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="18">
@@ -1277,7 +1298,7 @@
       </c>
       <c r="C34" s="20" t="n"/>
       <c r="D34" s="8" t="n">
-        <v>4576</v>
+        <v>6632.27</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="18">
@@ -1293,7 +1314,7 @@
       </c>
       <c r="C35" s="20" t="n"/>
       <c r="D35" s="8" t="n">
-        <v>6583.5</v>
+        <v>9541.860000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1303,6 +1324,10 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -1310,6 +1335,14 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
     <row r="50" ht="15.75" customHeight="1" s="18">
       <c r="A50" s="4" t="n"/>
     </row>
@@ -1318,16 +1351,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A9:D9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
+++ b/LISTAS/ma/TARUGO ESPIGA DISMAY.xlsx
@@ -1151,14 +1151,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45257.55651496706</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="18">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -1204,8 +1200,6 @@
       </c>
       <c r="E11" s="14" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
@@ -1213,12 +1207,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
@@ -1226,15 +1214,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="18" customHeight="1" s="18">
       <c r="A31" s="15" t="inlineStr">
         <is>
@@ -1266,7 +1245,7 @@
       </c>
       <c r="C32" s="20" t="n"/>
       <c r="D32" s="8" t="n">
-        <v>8370.049999999999</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="18">
@@ -1282,7 +1261,7 @@
       </c>
       <c r="C33" s="20" t="n"/>
       <c r="D33" s="10" t="n">
-        <v>6648.21</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="18">
@@ -1298,7 +1277,7 @@
       </c>
       <c r="C34" s="20" t="n"/>
       <c r="D34" s="8" t="n">
-        <v>6632.27</v>
+        <v>4576</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="18">
@@ -1314,7 +1293,7 @@
       </c>
       <c r="C35" s="20" t="n"/>
       <c r="D35" s="8" t="n">
-        <v>9541.860000000001</v>
+        <v>6583.5</v>
       </c>
     </row>
     <row r="36">
@@ -1324,10 +1303,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -1335,14 +1310,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
     <row r="50" ht="15.75" customHeight="1" s="18">
       <c r="A50" s="4" t="n"/>
     </row>
@@ -1351,16 +1318,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A9:D9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
